--- a/工事担任者問題20260512.xlsx
+++ b/工事担任者問題20260512.xlsx
@@ -2805,12 +2805,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>「クリティカルパスの所要日数は20日」が出たら✗→正しくは「21日」</t>
+          <t>「クリティカルパスの所要日数は20日」が出たら✗→正しくは21日ではなく23日</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>作業Dのトータルフロートは3日（選択肢3が正しい）。クリティカルパスの所要日数は21日（20日ではない）。クリティカルパスは問題の図から複数存在する場合がある。</t>
+          <t>クリティカルパスは①B③E⑥G⑦I⑧K（5+4+4+7+3=23日）および①C④H⑦I⑧K（3+10+7+3=23日）の複数パス。作業DのTFは「②最遅7日-②最早4日=3日」（選択肢3が正しい）。クリティカルパスは1本とは限らず複数存在する。</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>JIS C 0303:2000に規定される電話・情報設備の複合アウトレットの図記号は選択肢5の図記号。図記号と設備種別の対応を覚えること。</t>
+          <t>JIS C 0303:2000で規定される電話・情報設備の複合アウトレットの図記号は選択肢5（丸の中に×印の図記号）。選択肢1は電話用アウトレット（黒塗り長方形+丸）、選択肢2は情報用アウトレット（長方形+横線）、選択肢3は情報用アウトレット別表記（黒点+丸）、選択肢4はマルチメディアアウトレット（4マス長方形）。</t>
         </is>
       </c>
     </row>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>アローダイアグラムで作業Bがクリティカルパス上にある場合、作業Bが1日遅れるとクリティカルパスの所要日数は1日延びる（選択肢2が正しい）。作業A・G・Fがクリティカルパス外であれば遅延・短縮しても全体工期に影響しない。ダミー作業の有無は工期に影響しない。</t>
+          <t>クリティカルパスは①B③ダミー④F⑤H⑦I⑧（5+0+10+5+4=24日）。作業BはCP上のためTF=0であり1日遅れると全体も1日遅れる（選択肢2が正しい）。作業Gの⑧最早は24日・⑥最早は10日なのでFF=24-10-8=6日。作業A（TF=10日）・作業G（FF=6日）・クリティカルパスが複数存在するという記述はいずれも誤り。</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>A：アローダイアグラムで結合点番号5の最遅結合点時刻が9日（Aは正しい）。B：作業Dのフリーフロートが1日かどうかは図から計算する必要がある。データの正解1（Aのみ正しい）によりBのフリーフロートは1日ではない。</t>
+          <t>図2のアローダイアグラム: CP=①A②C④ダミー⑤E⑥G⑦（3+6+0+4+5=18日）。A：結合点⑤の最遅結合点時刻は9日（正しい）。B：作業DのFF=⑥最早-③最早-D=13-8-3=2日（「1日」は誤り）。よってAのみ正しい。</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>アローダイアグラムで作業Bを3日・作業Iを2日それぞれ短縮できるとき、両作業がクリティカルパス上にある場合はクリティカルパスの所要日数は最大4日短縮できる。短縮後の新たなクリティカルパスを確認することが重要。</t>
+          <t>クリティカルパスは①C④F⑤H⑦I⑧J（5+4+8+7+3=27日）。作業Bを3日・作業Iを2日短縮すると、新クリティカルパスは①C④F⑤H⑦I⑧J（5+4+8+5+3=25日）となり所要日数は4日短縮できる（正解4）。作業BのTF=2日なのでBの短縮分はCP短縮に直結しないが、Iの2日短縮がCPに反映される。</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>アローダイアグラムで作業Eのトータルフロートは2日。クリティカルパスの所要日数に影響を及ぼさない条件での最大許容遅れはトータルフロートに等しいため、作業Eは最大2日の遅れまで許容できる。</t>
+          <t>図2のアローダイアグラム: CP=①B⑤F⑥I⑧K⑨（9+2+7+5=23日）。作業EのTF=L[⑥]-E[②]-E日数=11-5-4=2日。クリティカルパスに影響を及ぼさない条件での作業Eの最大遅れは2日。</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>JIS C 0303:2000に規定される電話・情報設備の情報用アウトレットの図記号は選択肢1の図記号。複合アウトレット（選択肢5）との違いに注意。</t>
+          <t>JIS C 0303:2000で規定される情報用アウトレットの図記号は選択肢1（丸の中に黒塗り長方形の図記号）。選択肢2は情報用アウトレット別表記（長方形+横線）、選択肢3は別の情報用（黒点+丸）、選択肢4はマルチメディアアウトレット（4マス長方形）、選択肢5は複合アウトレット（×印+丸）。</t>
         </is>
       </c>
     </row>
@@ -29738,7 +29738,7 @@
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>T568B規格でLANケーブル両端の結線において、一端のピン1・2が他端のピン2・1に接続される（ペア内の2線が左右反転している）配線誤りはリバースペアという。スプリットペアはペアが分割接続される誤り、クロスペアはペア同士が交差する誤り。</t>
+          <t>図1はツイストペアケーブルの結線において一端のピン1・2が他端でピン2・1に逆接続されている状態を示しており、これはリバースペアという配線不良。スプリットペアはペアが分割接続される誤り、クロスペアはペア同士が交差する誤り。</t>
         </is>
       </c>
     </row>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>アローダイアグラムで作業Fのトータルフロートを図から計算すると2日ではない（正確な計算は図が必要）。クリティカルパスの所要日数は21日・クリティカルパスは1つ・作業Dのトータルフロートは3日・作業Gのフリーフロートは1日はいずれも正しい記述として選択肢4が誤り。</t>
+          <t>図2のアローダイアグラム: CP=21日（1本のみ）。作業DのTF=3日・作業GのFF=1日はいずれも正しい。選択肢4「作業FのTFは2日」が誤りで選択肢4が正解。作業FのTFは2日ではない。</t>
         </is>
       </c>
     </row>
@@ -33761,7 +33761,7 @@
       </c>
       <c r="U367" t="inlineStr">
         <is>
-          <t>JIS C 0303:2000に規定される電話・情報設備の複合アウトレットの図記号は選択肢5の図記号。情報用アウトレット（選択肢1）との違いに注意。</t>
+          <t>JIS C 0303:2000で規定される電話・情報設備の複合アウトレットの図記号は選択肢5（丸の中に×印の図記号）。選択肢1は電話用アウトレット（黒塗り長方形+丸）、選択肢2は情報用アウトレット（長方形+横線）、選択肢3は別の情報用（黒点+丸）、選択肢4はマルチメディアアウトレット（4マス長方形）。</t>
         </is>
       </c>
     </row>
@@ -38970,7 +38970,7 @@
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>JIS Q 9024の数値データに対する技法の一つで各区間の度数に比例する面積の長方形を並べた図はヒストグラム。管理図は時系列に品質特性値をプロットした図、特性要因図は魚の骨型図、散布図は2変数の相関を示す図、パレート図は頻度順棒グラフ+累積折れ線。</t>
+          <t>図3は各区間の度数に比例する面積の長方形を並べたヒストグラム。図1は散布図（2変数の相関）、図2はパレート図（頻度順棒グラフ+累積折れ線）、図4は管理図（時系列に品質特性値をプロット）。選択肢3「各区間の度数に比例する面積の長方形を並べた図がヒストグラム」が正しい。</t>
         </is>
       </c>
     </row>
@@ -42826,7 +42826,7 @@
       </c>
       <c r="U468" t="inlineStr">
         <is>
-          <t>JIS C 0303:2000に規定される情報用アウトレットの図記号は選択肢5の図記号。r6_1_gijutsu_q4_イの情報用アウトレットと同じ問題。複合アウトレット（選択肢1）との違いに注意。</t>
+          <t>JIS C 0303:2000で規定される情報用アウトレットの図記号は選択肢5（丸の中に黒塗り長方形の図記号）。r7_2では選択肢の並び順が他年度と異なる点に注意。選択肢1は複合アウトレット（×印+丸）、選択肢2はマルチメディアアウトレット（4マス長方形）、選択肢3は別の情報用（黒点+丸）、選択肢4は情報用アウトレット別表記（長方形+横線）。</t>
         </is>
       </c>
     </row>
@@ -43454,12 +43454,12 @@
       </c>
       <c r="T475" t="inlineStr">
         <is>
-          <t>「aXのaの値を小さくするほど採算性は低下する」が出たら✗→正しくは「aの値を小さくするほど変動原価率が下がり採算性は向上する」</t>
+          <t>「変動原価率aを小さくするほど工事の採算性が低下する」が出たら✗→正しくは「aを小さくするほど採算性は向上する」</t>
         </is>
       </c>
       <c r="U475" t="inlineStr">
         <is>
-          <t>選択肢4：変動原価aXのaの値を小さくするほど施工出来高を上げたときの採算性は「向上（低下は誤り）」する（選択肢4が誤り）。固定原価F・変動原価aX・P点は損益分岐点・Xp以上で採算がとれる・Fを下げると損益分岐点を下げられるはいずれも正しい。</t>
+          <t>図1より損益分岐点PはY=XとY=F+aXの交点。Xp以上で採算がとれる状態。選択肢4：変動原価aXのaの値を小さくするほどY=F+aXの傾きが緩やかになり損益分岐点が左（低いXp）に移動して採算性は「向上（低下は誤り）」する（選択肢4が誤り）。固定原価F・Pは損益分岐点・Xp以上で採算・Fを下げると損益分岐点を下げられるはいずれも正しい。</t>
         </is>
       </c>
     </row>
@@ -43552,7 +43552,7 @@
       </c>
       <c r="U476" t="inlineStr">
         <is>
-          <t>アローダイアグラムで作業C・H・I・Jをそれぞれ1・2・1・2日短縮できるとき、クリティカルパスの所要日数は最大4日短縮できる（短縮後の新しいクリティカルパスを確認する必要がある）。</t>
+          <t>図2のアローダイアグラム: CP=①A②C④ダミー⑤H⑥ダミー⑦J⑧（2+4+0+5+0+5=16日）。作業C1日・H2日・I1日・J2日短縮後のCP=①A②C④ダミー⑤H⑥ダミー⑦J⑧（2+3+0+3+0+3=11日）および①B③E⑤H⑥ダミー⑦J⑧（2+3+3+0+3=11日）→12日。16-12=4日短縮。</t>
         </is>
       </c>
     </row>
